--- a/Lab_4/data/partB/param_optimization_process/v150_k40_s100_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v150_k40_s100_results.xlsx
@@ -518,46 +518,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>4</v>
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -591,16 +591,16 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,13 +646,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -677,19 +677,19 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
         <v>7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -698,25 +698,25 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
         <v>4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
         <v>6</v>
       </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -750,25 +750,25 @@
         <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -790,37 +790,37 @@
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -845,31 +845,31 @@
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>40</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>13</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>7</v>
-      </c>
-      <c r="I8" t="n">
-        <v>34</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>8</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
         <v>4</v>
@@ -885,46 +885,46 @@
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
       <c r="I9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -958,13 +958,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,22 +998,22 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1041,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -1062,19 +1062,19 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1102,16 +1102,16 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
         <v>2</v>
@@ -1120,13 +1120,13 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -1142,40 +1142,40 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
         <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
         <v>47</v>
@@ -1184,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -1200,16 +1200,16 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1227,13 +1227,13 @@
         <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,34 +1246,34 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
         <v>6</v>
       </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>6</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3</v>
-      </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>3</v>
@@ -1282,13 +1282,13 @@
         <v>2</v>
       </c>
       <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
         <v>2</v>
       </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
       <c r="P16" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12776,7 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12997,7 +12997,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13218,7 +13218,7 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17587,7 +17587,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20188,7 +20188,7 @@
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20545,7 +20545,7 @@
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20868,7 +20868,7 @@
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20936,7 +20936,7 @@
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21038,7 +21038,7 @@
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21293,7 +21293,7 @@
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21769,7 +21769,7 @@
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21820,7 +21820,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22007,7 +22007,7 @@
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22364,7 +22364,7 @@
       </c>
       <c r="C1239" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22500,7 @@
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22636,7 +22636,7 @@
       </c>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22755,7 +22755,7 @@
       </c>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="C1273" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23061,7 +23061,7 @@
       </c>
       <c r="C1280" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23146,7 +23146,7 @@
       </c>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -23180,7 +23180,7 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23639,7 +23639,7 @@
       </c>
       <c r="C1314" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23673,7 +23673,7 @@
       </c>
       <c r="C1316" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23775,7 +23775,7 @@
       </c>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="C1328" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24217,7 @@
       </c>
       <c r="C1348" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24489,7 +24489,7 @@
       </c>
       <c r="C1364" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24506,7 +24506,7 @@
       </c>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -24591,7 +24591,7 @@
       </c>
       <c r="C1370" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25101,7 +25101,7 @@
       </c>
       <c r="C1400" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25135,7 +25135,7 @@
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25509,7 +25509,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26002,7 +26002,7 @@
       </c>
       <c r="C1453" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
